--- a/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
+++ b/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who We Pursue" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Next 12 Months" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Language" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,13 +71,18 @@
       <sz val="14"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00A9772F"/>
+      <sz val="12"/>
+    </font>
+    <font>
       <i val="1"/>
-      <color rgb="001A1D20"/>
+      <color rgb="000F4C3A"/>
       <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="000F4C3A"/>
+      <color rgb="001A1D20"/>
       <sz val="11"/>
     </font>
     <font>
@@ -89,9 +95,9 @@
       <color rgb="00A9772F"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00A9772F"/>
-      <sz val="12"/>
+      <i val="1"/>
+      <color rgb="006B6660"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -110,6 +116,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000F4C3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -264,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -289,12 +300,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -311,15 +330,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -331,7 +349,10 @@
     <xf numFmtId="9" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1112,7 +1133,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
@@ -1122,24 +1143,24 @@
           <t>CMRPC (regional planning)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="35" t="n">
         <v>60000</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="36" t="n">
         <v>0.45</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="37">
         <f>IF(AND(ISNUMBER(D11),ISNUMBER(E11)),D11*E11,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
@@ -1149,24 +1170,24 @@
           <t>MRPC (regional planning)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="35" t="n">
         <v>50000</v>
       </c>
-      <c r="E12" s="33" t="n">
+      <c r="E12" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="37">
         <f>IF(AND(ISNUMBER(D12),ISNUMBER(E12)),D12*E12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
@@ -1176,24 +1197,24 @@
           <t>Warm municipal relationships (Sutton/Shrewsbury/Phillipston)</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="35" t="n">
         <v>35000</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="36" t="n">
         <v>0.6</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="37">
         <f>IF(AND(ISNUMBER(D13),ISNUMBER(E13)),D13*E13,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
@@ -1203,24 +1224,24 @@
           <t>Existing network</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>Strongest</t>
         </is>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="35" t="n">
         <v>25000</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="36" t="n">
         <v>0.65</v>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="37">
         <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),D14*E14,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>NOW</t>
         </is>
@@ -1230,24 +1251,24 @@
           <t>Fuss &amp; O'Neill (engineering)</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="35" t="n">
         <v>40000</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="37">
         <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),D15*E15,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Qualify</t>
         </is>
@@ -1257,24 +1278,24 @@
           <t>MVPC / other RPCs</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="35" t="n">
         <v>50000</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E16" s="36" t="n">
         <v>0.25</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="37">
         <f>IF(AND(ISNUMBER(D16),ISNUMBER(E16)),D16*E16,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>Qualify</t>
         </is>
@@ -1284,18 +1305,18 @@
           <t>Community Paradigm (municipal consulting)</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="35" t="n">
         <v>30000</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.25</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="37">
         <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17)),D17*E17,0)</f>
         <v/>
       </c>
@@ -1306,14 +1327,14 @@
           <t>ENGAGEMENT FLOW</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Signal → Fit → Map → Build → Sustain → Prove</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -1323,13 +1344,13 @@
           <t>A known trigger: turnover, a stalled project, a funding deadline, a capacity gap.</t>
         </is>
       </c>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="18" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="22" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
@@ -1339,13 +1360,13 @@
           <t>Confirm authority, budget, and that it's a known problem we solve.</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="18" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="22" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
@@ -1355,13 +1376,13 @@
           <t>A paid Stewardship Map — the entry move.</t>
         </is>
       </c>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="18" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="22" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
@@ -1371,13 +1392,13 @@
           <t>Deliver the project, funding, permit, implementation, or capacity work.</t>
         </is>
       </c>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Sustain</t>
         </is>
@@ -1387,13 +1408,13 @@
           <t>Transfer ownership; optional Implementation or Capacity Support.</t>
         </is>
       </c>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="18" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="22" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Prove</t>
         </is>
@@ -1403,10 +1424,10 @@
           <t>Capture the evidence — which becomes the next Signal.</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="18" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1546,7 +1567,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Three questions to keep answering:  (1) Which 5 targets are we actually pursuing this quarter?  (2) What is the first paid engagement we want to sell?  (3) Which transfer asset gets created every time we do it?</t>
         </is>
@@ -1556,6 +1577,219 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A12:C13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Language Guardrails — Do Not Say</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Protect the category. We sell outcomes and stewardship — never hype, never software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Don't say</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Say instead</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>AI-powered / AI transformation</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Continuity &amp; Stewardship Systems · institutional stewardship</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Too hype-driven; misstates the work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Revolutionary / disruptive</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Serious, useful, durable</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Generic startup language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Software platform / SaaS</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Hosted operating environment</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Makes the method sound like generic software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>The dashboard (as the product)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>The Stewardship Map / the operating environment</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>A dashboard is only a view, not the product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Workflow engine</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Governance Process Runtime (PuddleJumper)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>It governs the conditions around work, not just steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>AI bot</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Governance Steward (the human guide)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Keep the human trust layer intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>We automate everything / magic</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>We make the work easier to understand and continue</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Overclaim and wrong emphasis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Fully solved</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Visible, improved, stewarded</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Overpromises; denies the reality of stewardship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Buy PuddleJumper / the workbench</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Clients receive the tool, framework, brief, or operating layer</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Don't make internal build infrastructure the product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>Tagline, if you need one beneath the wordmark:  Continuity • Data • Stewardship.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A14:C14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1567,7 +1801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1617,22 +1851,46 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>The way we say it: most organizations don't suffer from a lack of effort. They suffer from a lack of visibility. PublicLogic exists to solve that problem.</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>North Star</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>“Every system should make it easier for the next person to do the right thing.”</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Vision:  organizations should be easier to inherit than they were to build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Legacy line:  Honor the past. Improve the present. Continue the work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>This isn't a new company we're inventing. It's the company that already exists — named, and made repeatable.</t>
         </is>
@@ -1649,7 +1907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1767,16 +2025,24 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>It's quiet failure. By the time anyone notices, the momentum, the money, or the knowledge is already gone. Stewardship is how we keep that from happening.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>The governance frame:  the central question is not whether risk exists, but where it will live.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1788,7 +2054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1841,122 +2107,153 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>What we are NOT</t>
+          <t>Core promise</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Not a grant-writing firm. Not an AI consulting firm. Not a software company. Not a planning firm. Not a generic implementation consultant. The work touches all of those, but none of them is the point.</t>
+          <t>We do not create dependency. We create understanding.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Clients buy / we deliver</t>
+          <t>What we are NOT</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Clients buy funding, progress, and capacity. We deliver those — plus the stewardship that makes them last. That's not a contradiction; it's the business model.</t>
+          <t>Not a grant-writing firm. Not an AI consulting firm. Not a software company. Not a planning firm. Not a generic implementation consultant. The work touches all of those, but none of them is the point.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Clients buy / we deliver</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Clients buy funding, progress, and capacity. We deliver those — plus the stewardship that makes them last. That's not a contradiction; it's the business model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>How we deliver</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>PublicLogic delivers services through Continuity &amp; Stewardship Systems designed to preserve knowledge, accountability, continuity, and momentum. (Defined once on the Transfer tab — it's the plumbing, not a product.)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>THE EQUATION</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Recommended (use this one):  Good Work + Stewardship = Work That Lasts</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Fuller / operational:  Project + Funding + Capacity + Continuity = Implementation</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Fuller / outcomes:  Vision + Funding + Capacity + Stewardship = Durable Results</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>HOW WE WORK</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>Map  →  Embed  →  Encode  →  Sustain</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Map</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Surface how work, knowledge, authority, records, and risk actually move.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Embed</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Put the right structure into the live workflow, with the people who do the work.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Encode</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Capture the knowledge and rules so they outlast any individual.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Sustain</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Monitor adoption and transfer ownership so it runs without us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>THE ENGAGEMENT CYCLE</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Discover · Honor · Understand · Improve · Build · Steward · Continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Map → Embed → Encode → Sustain is the method; this is the cycle a client moves through with us. (The Operating Workbook follows it tab for tab.)</t>
         </is>
       </c>
     </row>
@@ -1971,7 +2268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2185,7 +2482,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Implementation vs Capacity: Implementation helps YOUR team execute — the work stays theirs (e.g., Shrewsbury). Capacity means we hold the role ourselves until it transfers back (e.g., Swanzey). Same discipline; different level of who holds the Chair.</t>
         </is>
@@ -2193,17 +2490,26 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Entry below the Map: the Permit &amp; Bridge tab adds a public-facing ladder — Tier 0 Public Permit Helper (free / very low cost) and Tier 1 Permit Path Scan ($250–$750) — that builds trust and feeds these paid offers.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Deeper engagement: when a Map reveals serious drift or transition risk, the next step up is a Diagnostic — a deep review of risks, records, structure, and next steps ($10,000–$25,000+). It sits between the Map and ongoing support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A13:E14"/>
     <mergeCell ref="A11:E12"/>
+    <mergeCell ref="A15:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2373,22 +2679,22 @@
           <t>LogicCommons — the public access layer</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="18" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="22" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Free templates, checklists, and frameworks that help people understand the path before they need paid help.   LogicCommons helps people start. PublicLogic helps them carry it through.</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="21" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="25" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="n"/>
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="24" t="n"/>
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="28" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2448,7 +2754,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>This layer should be low-cost or free — its purpose is access, trust, and triage. It does NOT replace the municipality, inspector, planner, or permitting authority. It helps people ask better questions, gather the right information, and avoid wasting time.</t>
         </is>
@@ -2556,7 +2862,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>LogicCommons helps people start. PublicLogic helps them carry it through.</t>
         </is>
@@ -2689,7 +2995,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>Credit policy: a paid tier credits toward the next engagement, but credits don't stack — up to one tier's fee credits forward. Keeps the entry risk low without eroding margin on a follow-on sprint.</t>
         </is>
@@ -2697,7 +3003,7 @@
     </row>
     <row r="54"/>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>Permit &amp; Bridge helps the public understand the path and helps project sponsors move through it.  That's the full product.</t>
         </is>
@@ -2891,7 +3197,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Honesty note: confirm what we're comfortable naming before sharing externally — some of this is client-confidential.</t>
         </is>
@@ -2947,7 +3253,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>How people, roles, adoption, leadership, and change actually work — and why systems get used or ignored.</t>
+          <t>How people, roles, adoption, leadership, and change actually work — and why systems get used or ignored. In the model this is the Governance Steward lane: the human-centered guide who makes systems fit real people and keeps them trusted, adopted, and reviewed over time.</t>
         </is>
       </c>
     </row>
@@ -3075,21 +3381,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>PublicLogic should be stronger after every engagement.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>The client should be less dependent after every engagement.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>If neither happens, we are doing consulting instead of stewardship.</t>
         </is>
@@ -3119,22 +3425,22 @@
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>May include:</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>CaseSpaces · Workbooks · Registers · Templates · VAULT records · Accountability structures · Continuity plans · Project environments · Proof frameworks.   (Under the hood these run on PuddleJumper — no one needs that name unless they want to go deeper. LogicCommons is the separate public, free layer.)</t>
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>CaseSpaces · Workbooks · Registers · Templates · VAULT records · Accountability structures · Continuity plans · Project environments · Proof frameworks.   (Under the hood these run on PuddleJumper — our Governance Process Runtime; no one needs that name unless they want to go deeper. VAULT = Verification · Authority · Utility · Legitimacy · Transfer. LogicCommons is the separate public, free layer.)</t>
         </is>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>A client never has to care about the components. They care about one thing: “If my planner leaves, does this still work?” A Continuity &amp; Stewardship System is how we answer yes.</t>
         </is>

--- a/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
+++ b/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -113,9 +113,6 @@
     <font>
       <color rgb="006B6660"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -275,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -343,14 +340,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="17" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -795,7 +785,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>LogicCommons = public access layer · Permit &amp; Bridge = navigation layer · PublicLogic = services · Continuity &amp; Stewardship Systems = how we deliver (records, processes, templates, environments, accountability).</t>
+          <t>Five layers, five verbs:  LogicCommons = Understand · Permit &amp; Bridge = Navigate · Stewardship Map = Diagnose · PublicLogic = Deliver · Continuity &amp; Stewardship Systems = Sustain.</t>
         </is>
       </c>
     </row>
@@ -1003,12 +993,10 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1096,229 +1084,184 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TIER-1 PIPELINE  (illustrative Revenue/Probability — replace with real figures; Weighted = Revenue x Probability; sort to rank)</t>
+          <t>TIER-1 PIPELINE  (no revenue estimates until they're real — track relationship, probability, and the next action)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Pursue</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Relationship</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Revenue ($)</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Weighted ($)</t>
+          <t>Next action</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>CMRPC (regional planning)</t>
         </is>
       </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Developing</t>
+        </is>
+      </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>Book an intro call; offer a paid Stewardship Map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MRPC (regional planning)</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="D11" s="35" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F11" s="37">
-        <f>IF(AND(ISNUMBER(D11),ISNUMBER(E11)),D11*E11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>MRPC (regional planning)</t>
-        </is>
-      </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>Developing</t>
-        </is>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E12" s="36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F12" s="37">
-        <f>IF(AND(ISNUMBER(D12),ISNUMBER(E12)),D12*E12,0)</f>
-        <v/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>Warm intro; share the one-pager.</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Warm municipal relationships (Sutton/Shrewsbury/Phillipston)</t>
         </is>
       </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>35000</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F13" s="37">
-        <f>IF(AND(ISNUMBER(D13),ISNUMBER(E13)),D13*E13,0)</f>
-        <v/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>Propose a Map on a known stalled function.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Existing network</t>
         </is>
       </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Strongest</t>
+        </is>
+      </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>Strongest</t>
-        </is>
-      </c>
-      <c r="D14" s="35" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E14" s="36" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F14" s="37">
-        <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),D14*E14,0)</f>
-        <v/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>Ask directly who needs a Map first.</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>NOW</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Fuss &amp; O'Neill (engineering)</t>
         </is>
       </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>Find a warm intro before pursuing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>MVPC / other RPCs</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D15" s="35" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F15" s="37">
-        <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),D15*E15,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>Qualify</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>MVPC / other RPCs</t>
-        </is>
-      </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>Qualify only once Tier 1 is producing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Community Paradigm (municipal consulting)</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
           <t>Cold</t>
         </is>
       </c>
-      <c r="D16" s="35" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F16" s="37">
-        <f>IF(AND(ISNUMBER(D16),ISNUMBER(E16)),D16*E16,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>Qualify</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Community Paradigm (municipal consulting)</t>
-        </is>
-      </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F17" s="37">
-        <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17)),D17*E17,0)</f>
-        <v/>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>Qualify only once Tier 1 is producing.</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1432,10 +1375,10 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A9:F9"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="B22:F22"/>
   </mergeCells>
@@ -1588,7 +1531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1781,7 +1724,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="38" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Institutional Stewardship (by itself)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Preventing turnover, lost knowledge, stalled projects, and missed opportunities through Institutional Stewardship</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Always return to the problem. Stewardship disconnected from a real pain point goes abstract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Tagline, if you need one beneath the wordmark:  Continuity • Data • Stewardship.</t>
         </is>
@@ -1789,7 +1749,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
+++ b/docs/business/final_deck/PublicLogic_v1_Business_Stack/PublicLogic - Capabilities Workbook (v2.0 2026-06).xlsx
@@ -2452,7 +2452,7 @@
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Entry below the Map: the Permit &amp; Bridge tab adds a public-facing ladder — Tier 0 Public Permit Helper (free / very low cost) and Tier 1 Permit Path Scan ($250–$750) — that builds trust and feeds these paid offers.</t>
+          <t>Entry below the Map: the Permit &amp; Bridge tab adds a public-facing ladder — Tier 0 Public Permit Helper (free / very low cost) and Tier 1 Permit Path Scan ($500 flat) — that builds trust and feeds these paid offers.</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>$250 – $750</t>
+          <t>$500 flat</t>
         </is>
       </c>
     </row>
